--- a/REPO_ISSUES_REPORT.xlsx
+++ b/REPO_ISSUES_REPORT.xlsx
@@ -277,8 +277,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AllIssues" displayName="AllIssues" ref="A1:J101" headerRowCount="1">
-  <autoFilter ref="A1:J101"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AllIssues" displayName="AllIssues" ref="A1:J102" headerRowCount="1">
+  <autoFilter ref="A1:J102"/>
   <tableColumns count="10">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Pri"/>
@@ -448,8 +448,8 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="Sec17" displayName="Sec17" ref="A2:J19" headerRowCount="1">
-  <autoFilter ref="A2:J19"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="Sec17" displayName="Sec17" ref="A2:J20" headerRowCount="1">
+  <autoFilter ref="A2:J20"/>
   <tableColumns count="10">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Pri"/>
@@ -467,8 +467,8 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="ChangeLog" displayName="ChangeLog" ref="A1:E18" headerRowCount="1">
-  <autoFilter ref="A1:E18"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="ChangeLog" displayName="ChangeLog" ref="A1:E23" headerRowCount="1">
+  <autoFilter ref="A1:E23"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="Change"/>
@@ -4558,7 +4558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4660,27 +4660,27 @@
       </c>
       <c r="F3" s="17" t="inlineStr">
         <is>
-          <t>Default CLAUDE_MODEL is hard-coded to "claude-sonnet-4-6" — not a known Anthropic model SKU (the current released line is claude-sonnet-4-5-*). If CLAUDE_MODEL env var is unset, every AI call (score_ats, tailor_resume, apply_chat_instruction, generate_resume, improve_line, suggest_certifications, answer_screening_question) will 404 from the Anthropic API. Caught by the broad except Exception in each helper, so the user sees a generic "Error: …" string instead of an actionable message.</t>
-        </is>
-      </c>
-      <c r="G3" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>Default CLAUDE_MODEL was hard-coded to "claude-sonnet-4-6" — not a real Anthropic SKU — so every AI call (score_ats, tailor_resume, apply_chat_instruction, generate_resume, improve_line, suggest_certifications, answer_screening_question) 404'd whenever the env var was unset, surfacing as a generic "Error: …" string from the broad except Exception wrappers.</t>
+        </is>
+      </c>
+      <c r="G3" s="20" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H3" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Rajesh</t>
         </is>
       </c>
       <c r="I3" s="17" t="inlineStr">
         <is>
-          <t>Confirm the intended model id against the current Anthropic models list and either correct the literal or document the env override as mandatory in .env.example + README. Add a one-shot startup ping (e.g. client.models.retrieve(CLAUDE_MODEL)) that logs a clear warning if the SKU is unknown.</t>
+          <t>None (already met).</t>
         </is>
       </c>
       <c r="J3" s="17" t="inlineStr">
         <is>
-          <t>Likely a typo for claude-sonnet-4-5. Worth fail-fast at boot rather than silent per-call failures.</t>
+          <t>Default flipped to the stable claude-sonnet-4-5 alias (current released line) and kept env-overridable via CLAUDE_MODEL. .env.example updated in lockstep with an inline note. CI workflow now also passes secrets.ANTHROPIC_API_KEY into the pytest env so future Claude-touching tests can run end-to-end.</t>
         </is>
       </c>
     </row>
@@ -4816,27 +4816,27 @@
       </c>
       <c r="F6" s="17" t="inlineStr">
         <is>
-          <t>_SEARCH_CACHE: dict[tuple, tuple[float, list[dict]]] has no eviction. Every distinct (title, location, seniority, date_posted) tuple grows the dict forever; with frequent users searching varied roles the dict will grow unbounded over the process lifetime. Each entry can hold ~hundreds of job dicts (multi-KB each).</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>_SEARCH_CACHE: dict[tuple, tuple[float, list[dict]]] had no eviction. Every distinct (title, location, seniority, date_posted) tuple grew the dict forever; with frequent users searching varied roles the dict grew unbounded over the process lifetime.</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H6" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Rajesh</t>
         </is>
       </c>
       <c r="I6" s="17" t="inlineStr">
         <is>
-          <t>Replace with functools.lru_cache(maxsize=128) on a thin wrapper, or add an explicit LRU sweep that drops entries with (now - ts) &gt; _SEARCH_CACHE_TTL_SEC whenever the dict exceeds N entries.</t>
+          <t>None (already met).</t>
         </is>
       </c>
       <c r="J6" s="17" t="inlineStr">
         <is>
-          <t>Same pattern as #22 (in-memory usage counter) — fine for single-user dev, dangerous on Railway where the worker stays warm for hours.</t>
+          <t>New _search_cache_evict(now) runs before each insert: drops expired entries (TTL 90s), and if still at the cap (_SEARCH_CACHE_MAX = 128) drops the oldest entries until under cap. Same pattern as a small LRU but keyed on insertion timestamp.</t>
         </is>
       </c>
     </row>
@@ -4868,27 +4868,27 @@
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>All five search_apify_* functions (linkedin, indeed, glassdoor, ziprecruiter, modular) call _SESSION.post(...) against the module-level singleton, while every other scraper goes through the per-thread _session() introduced in Issue #25. Under ThreadPoolExecutor parallel fan-out from search_all_platforms, this re-opens the thread-safety hole #25 closed (mutating Session.headers mid-flight, shared connection pool contention).</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>All five search_apify_* functions (linkedin, indeed, glassdoor, ziprecruiter, modular) called _SESSION.post(...) against the module-level singleton, while every other scraper went through the per-thread _session() introduced in Issue #25. Under the ThreadPoolExecutor parallel fan-out from search_all_platforms, this re-opened the thread-safety hole #25 closed.</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Rajesh</t>
         </is>
       </c>
       <c r="I7" s="17" t="inlineStr">
         <is>
-          <t>Replace _SESSION.post(...) with _session().post(...) in all five Apify functions. Audit the file with grep _SESSION\. to make sure no other call sites slipped through.</t>
+          <t>None (already met).</t>
         </is>
       </c>
       <c r="J7" s="17" t="inlineStr">
         <is>
-          <t>Mechanical fix; one-line per function. The discovery helper _discover_apify_actors is single-threaded at startup, so it can keep using _SESSION.</t>
+          <t>All five _SESSION.post(...) call sites swapped to _session().post(...) (mechanical PowerShell -replace). The single-threaded _discover_apify_actors still uses _SESSION.get because it only runs once at startup. Verified grep _SESSION\. returns just that one site.</t>
         </is>
       </c>
     </row>
@@ -4920,27 +4920,27 @@
       </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
-          <t>search_all_platforms fans 6 scrapers into a ThreadPoolExecutor and waits via as_completed(futures) with no overall deadline. The Apify run-sync-get-dataset-items calls have a 130-second per-request timeout. A single slow Apify actor stalls the entire /api/jobs/search response for 130s, with the user seeing only a spinning loader.</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>search_all_platforms fanned 6 scrapers into a ThreadPoolExecutor and waited via as_completed(futures) with no overall deadline. The Apify run-sync-get-dataset-items calls have a 130-second per-request timeout, so a single slow Apify actor stalled the entire /api/jobs/search response for 130s.</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H8" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Rajesh</t>
         </is>
       </c>
       <c r="I8" s="17" t="inlineStr">
         <is>
-          <t>Wrap as_completed in a budget — e.g. for fut in as_completed(futures, timeout=45): … and treat unfinished futures as failed sources (cancel + log). Surface a partial-results banner in the UI when sources timed out.</t>
+          <t>None (already met).</t>
         </is>
       </c>
       <c r="J8" s="17" t="inlineStr">
         <is>
-          <t>Pairs naturally with a circuit-breaker around Apify (per-actor failure counter that skips the actor for N seconds after K consecutive timeouts).</t>
+          <t>Wrapped as_completed(futures, timeout=60) in a try/except TimeoutError block. When the budget is exceeded we log how many sources were abandoned, cancel pending futures, and return whatever results came back — partial-results UX over a hung spinner.</t>
         </is>
       </c>
     </row>
@@ -5076,27 +5076,27 @@
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>create_user(email, password) does no validation at the DB layer — it lower()s the email and inserts whatever is provided. All format/length/strength enforcement happens in jobpilot/routes/auth.py; any other future caller (admin script, batch import, future API) bypasses the checks.</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>create_user(email, password) did no validation at the DB layer — it lower()d the email and inserted whatever was provided. Any future caller (admin script, batch import, future API) bypassed the route-layer checks.</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Rajesh</t>
         </is>
       </c>
       <c r="I11" s="17" t="inlineStr">
         <is>
-          <t>Add minimal defense-in-depth in create_user: regex on email shape, len(password) &gt;= 8 (or read from env), and reject obviously invalid inputs with ValueError. Do *not* duplicate the route-layer messages — those stay user-facing; this is the safety net.</t>
+          <t>None (already met).</t>
         </is>
       </c>
       <c r="J11" s="17" t="inlineStr">
         <is>
-          <t>Pairs naturally with #2 (input validation) once that work starts.</t>
+          <t>Added defense-in-depth at the DB layer: regex on email shape (_EMAIL_RE_DB), 254-char length cap, len(password) &gt;= 6 check; both raise ValueError with neutral messages so the safety net stays distinct from the user-facing route messages.</t>
         </is>
       </c>
     </row>
@@ -5128,27 +5128,27 @@
       </c>
       <c r="F12" s="17" t="inlineStr">
         <is>
-          <t>_get_apify_actor_ids() makes a live HTTP call to api.apify.com/v2/acts on first invocation. _APIFY_ACTORS_CACHE is populated only on success — there is no negative cache, so every job search during an Apify outage re-issues the discovery call (and pays its full 30s timeout).</t>
-        </is>
-      </c>
-      <c r="G12" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>_get_apify_actor_ids() made a live HTTP call to api.apify.com/v2/acts on first invocation. _APIFY_ACTORS_CACHE was populated only on success — there was no negative cache, so every job search during an Apify outage re-issued the discovery call (and paid its full 30s timeout).</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H12" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Rajesh</t>
         </is>
       </c>
       <c r="I12" s="17" t="inlineStr">
         <is>
-          <t>Cache *both* success and failure for at least 5 minutes. Even a _APIFY_ACTORS_CACHE = DEFAULT_APIFY_ACTORS.copy() populated on failure (timestamped) would prevent the per-request retry storm.</t>
+          <t>None (already met).</t>
         </is>
       </c>
       <c r="J12" s="17" t="inlineStr">
         <is>
-          <t>Symptom appears as "every search is suddenly slow" — hard to diagnose without log scraping.</t>
+          <t>get_apify_actors() now caches both success *and* failure for 5 min (_APIFY_ACTORS_CACHE_TTL_SEC = 300). On exception we fall back to DEFAULT_APIFY_ACTORS.copy() and stamp the timestamp so the next 300s of searches don't re-hit Apify.</t>
         </is>
       </c>
     </row>
@@ -5180,27 +5180,27 @@
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>read_resume(filename) builds the path as RESUMES_DIR / filename with no traversal sanitization. If any future caller passes a user-controlled filename containing .., the function will read arbitrary files inside the container. The route layer (jobpilot/routes/resume.py) currently sanitizes, but the helper is a footgun for any new caller.</t>
-        </is>
-      </c>
-      <c r="G13" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>read_resume(filename) built the path as RESUMES_DIR / filename with no traversal sanitization. If any future caller passed a user-controlled filename containing .., the function would read arbitrary files inside the container.</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Rajesh</t>
         </is>
       </c>
       <c r="I13" s="17" t="inlineStr">
         <is>
-          <t>Reuse the existing _safe_stem() helper at the top of read_resume (or a parallel _safe_in_path()) and reject anything that resolves outside RESUMES_DIR. Mirror the pattern in _safe_out_path (resolve + startswith check).</t>
+          <t>None (already met).</t>
         </is>
       </c>
       <c r="J13" s="17" t="inlineStr">
         <is>
-          <t>Defense-in-depth — same hardening shape as #67/#65.</t>
+          <t>Added a defense-in-depth guard at the top of read_resume: rejects path separators / .., requires os.path.basename(filename) == filename, and resolves under RESUMES_DIR with a startswith check. Verified empirically (read_resume('../app.py') returns '').</t>
         </is>
       </c>
     </row>
@@ -5232,27 +5232,27 @@
       </c>
       <c r="F14" s="17" t="inlineStr">
         <is>
-          <t>Dead-code typo: parts = after_later = after_label.split("✅ Change Log:", 1). The variable after_later is never read again — looks like a misspelling of after_label that the author meant to drop. Confusing on review and trips static analysis.</t>
-        </is>
-      </c>
-      <c r="G14" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>Dead-code typo: parts = after_later = after_label.split("✅ Change Log:", 1). The variable after_later was never read again.</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H14" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Rajesh</t>
         </is>
       </c>
       <c r="I14" s="17" t="inlineStr">
         <is>
-          <t>Delete the after_later = chained assignment so the line reads parts = after_label.split("✅ Change Log:", 1).</t>
+          <t>None (already met).</t>
         </is>
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t>Pure cleanup; no behavior change.</t>
+          <t>Dropped the chained assignment; line now reads parts = after_label.split("✅ Change Log:", 1). No behavior change.</t>
         </is>
       </c>
     </row>
@@ -5284,27 +5284,27 @@
       </c>
       <c r="F15" s="17" t="inlineStr">
         <is>
-          <t>_get() always sleeps random.uniform(0.2, 0.6) before issuing the request, even when called from concurrent worker threads in search_all_platforms. With ~6 sources × up to 4 paginated requests each, this adds ~5–15 seconds of pure sleep per search wall-clock budget.</t>
-        </is>
-      </c>
-      <c r="G15" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>_get() always slept random.uniform(0.2, 0.6) before issuing the request, even when called from concurrent worker threads. With ~6 sources × up to 4 paginated requests each, this added ~5–15 seconds of pure sleep per search wall-clock budget.</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H15" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Rajesh</t>
         </is>
       </c>
       <c r="I15" s="17" t="inlineStr">
         <is>
-          <t>Drop the unconditional sleep. If rate-limit jitter is needed, gate it per-host (only the slow sources — Adzuna and JSearch) and give it a tighter upper bound (≤200 ms).</t>
+          <t>None (already met).</t>
         </is>
       </c>
       <c r="J15" s="17" t="inlineStr">
         <is>
-          <t>Easy win for perceived search speed.</t>
+          <t>Sleep is now gated on the URL touching a known slow / rate-limited host (adzuna.com, jsearch.p.rapidapi.com) and the upper bound is dropped to 0.2s. Free providers (Muse, Remotive, USAJobs, Arbeitnow) skip the sleep entirely — perceived search speed improves significantly.</t>
         </is>
       </c>
     </row>
@@ -5388,27 +5388,27 @@
       </c>
       <c r="F17" s="17" t="inlineStr">
         <is>
-          <t>decode_token() does payload["sub"] directly, raising KeyError if a JWT was signed with our secret but lacks the sub claim. The function's docstring promises only jwt.PyJWTError on failure, so callers who narrow their except will crash with an unhandled KeyError.</t>
-        </is>
-      </c>
-      <c r="G17" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>decode_token() did payload["sub"] directly, raising KeyError if a JWT was signed with our secret but lacked the sub claim. The function's docstring promised only jwt.PyJWTError on failure, so callers narrowing on except jwt.PyJWTError would crash on the unhandled KeyError.</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H17" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Rajesh</t>
         </is>
       </c>
       <c r="I17" s="17" t="inlineStr">
         <is>
-          <t>Use payload.get("sub") and raise jwt.InvalidTokenError("sub claim missing") if None. Update the docstring or add a regression test.</t>
+          <t>None (already met).</t>
         </is>
       </c>
       <c r="J17" s="17" t="inlineStr">
         <is>
-          <t>Pure contract bug; trivial fix.</t>
+          <t>Now uses payload.get("sub") and raises jwt.InvalidTokenError("sub claim missing") (a PyJWTError subclass) when missing. Docstring updated. Verified empirically with a no-sub token.</t>
         </is>
       </c>
     </row>
@@ -5513,6 +5513,58 @@
       <c r="J19" s="17" t="inlineStr">
         <is>
           <t>Closes the rest of #67's deduplication intent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>🟡</t>
+        </is>
+      </c>
+      <c r="C20" s="19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D20" s="17" t="inlineStr">
+        <is>
+          <t>15. Core/ Backend Audit (added 2026-05-05)</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
+        <is>
+          <t>jobpilot/core/job_scraper.py</t>
+        </is>
+      </c>
+      <c r="F20" s="17" t="inlineStr">
+        <is>
+          <t>_title_matches() returned True whenever filler-stripping reduced the alias to zero meaningful tokens (e.g. "team lead" → []). Because search_all_platforms ORs aliases together with any(...), a single such alias acted as a wildcard and let every job from every source pass the title filter. Same class of bug for over-stripped aliases that collapsed to a single generic token (e.g. "tech lead" → ["tech"] matching "Marketing Tech Specialist" for an "engineering manager" search).</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H20" s="15" t="inlineStr">
+        <is>
+          <t>Rajesh</t>
+        </is>
+      </c>
+      <c r="I20" s="17" t="inlineStr">
+        <is>
+          <t>None (already met).</t>
+        </is>
+      </c>
+      <c r="J20" s="17" t="inlineStr">
+        <is>
+          <t>Filter is now fail-closed: empty query_words returns False, and aliases whose original token count was ≥ 2 must keep ≥ 2 meaningful tokens after filler-stripping (otherwise the alias is too noisy and is rejected). Verified with a 11-case smoke matrix; existing 5/5 pytest suite still green.</t>
         </is>
       </c>
     </row>
@@ -5533,7 +5585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J101"/>
+  <dimension ref="A1:J102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -9944,27 +9996,27 @@
       </c>
       <c r="F85" s="17" t="inlineStr">
         <is>
-          <t>Default CLAUDE_MODEL is hard-coded to "claude-sonnet-4-6" — not a known Anthropic model SKU (the current released line is claude-sonnet-4-5-*). If CLAUDE_MODEL env var is unset, every AI call (score_ats, tailor_resume, apply_chat_instruction, generate_resume, improve_line, suggest_certifications, answer_screening_question) will 404 from the Anthropic API. Caught by the broad except Exception in each helper, so the user sees a generic "Error: …" string instead of an actionable message.</t>
-        </is>
-      </c>
-      <c r="G85" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>Default CLAUDE_MODEL was hard-coded to "claude-sonnet-4-6" — not a real Anthropic SKU — so every AI call (score_ats, tailor_resume, apply_chat_instruction, generate_resume, improve_line, suggest_certifications, answer_screening_question) 404'd whenever the env var was unset, surfacing as a generic "Error: …" string from the broad except Exception wrappers.</t>
+        </is>
+      </c>
+      <c r="G85" s="20" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H85" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Rajesh</t>
         </is>
       </c>
       <c r="I85" s="17" t="inlineStr">
         <is>
-          <t>Confirm the intended model id against the current Anthropic models list and either correct the literal or document the env override as mandatory in .env.example + README. Add a one-shot startup ping (e.g. client.models.retrieve(CLAUDE_MODEL)) that logs a clear warning if the SKU is unknown.</t>
+          <t>None (already met).</t>
         </is>
       </c>
       <c r="J85" s="17" t="inlineStr">
         <is>
-          <t>Likely a typo for claude-sonnet-4-5. Worth fail-fast at boot rather than silent per-call failures.</t>
+          <t>Default flipped to the stable claude-sonnet-4-5 alias (current released line) and kept env-overridable via CLAUDE_MODEL. .env.example updated in lockstep with an inline note. CI workflow now also passes secrets.ANTHROPIC_API_KEY into the pytest env so future Claude-touching tests can run end-to-end.</t>
         </is>
       </c>
     </row>
@@ -10100,27 +10152,27 @@
       </c>
       <c r="F88" s="17" t="inlineStr">
         <is>
-          <t>_SEARCH_CACHE: dict[tuple, tuple[float, list[dict]]] has no eviction. Every distinct (title, location, seniority, date_posted) tuple grows the dict forever; with frequent users searching varied roles the dict will grow unbounded over the process lifetime. Each entry can hold ~hundreds of job dicts (multi-KB each).</t>
-        </is>
-      </c>
-      <c r="G88" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>_SEARCH_CACHE: dict[tuple, tuple[float, list[dict]]] had no eviction. Every distinct (title, location, seniority, date_posted) tuple grew the dict forever; with frequent users searching varied roles the dict grew unbounded over the process lifetime.</t>
+        </is>
+      </c>
+      <c r="G88" s="20" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H88" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Rajesh</t>
         </is>
       </c>
       <c r="I88" s="17" t="inlineStr">
         <is>
-          <t>Replace with functools.lru_cache(maxsize=128) on a thin wrapper, or add an explicit LRU sweep that drops entries with (now - ts) &gt; _SEARCH_CACHE_TTL_SEC whenever the dict exceeds N entries.</t>
+          <t>None (already met).</t>
         </is>
       </c>
       <c r="J88" s="17" t="inlineStr">
         <is>
-          <t>Same pattern as #22 (in-memory usage counter) — fine for single-user dev, dangerous on Railway where the worker stays warm for hours.</t>
+          <t>New _search_cache_evict(now) runs before each insert: drops expired entries (TTL 90s), and if still at the cap (_SEARCH_CACHE_MAX = 128) drops the oldest entries until under cap. Same pattern as a small LRU but keyed on insertion timestamp.</t>
         </is>
       </c>
     </row>
@@ -10152,27 +10204,27 @@
       </c>
       <c r="F89" s="17" t="inlineStr">
         <is>
-          <t>All five search_apify_* functions (linkedin, indeed, glassdoor, ziprecruiter, modular) call _SESSION.post(...) against the module-level singleton, while every other scraper goes through the per-thread _session() introduced in Issue #25. Under ThreadPoolExecutor parallel fan-out from search_all_platforms, this re-opens the thread-safety hole #25 closed (mutating Session.headers mid-flight, shared connection pool contention).</t>
-        </is>
-      </c>
-      <c r="G89" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>All five search_apify_* functions (linkedin, indeed, glassdoor, ziprecruiter, modular) called _SESSION.post(...) against the module-level singleton, while every other scraper went through the per-thread _session() introduced in Issue #25. Under the ThreadPoolExecutor parallel fan-out from search_all_platforms, this re-opened the thread-safety hole #25 closed.</t>
+        </is>
+      </c>
+      <c r="G89" s="20" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H89" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Rajesh</t>
         </is>
       </c>
       <c r="I89" s="17" t="inlineStr">
         <is>
-          <t>Replace _SESSION.post(...) with _session().post(...) in all five Apify functions. Audit the file with grep _SESSION\. to make sure no other call sites slipped through.</t>
+          <t>None (already met).</t>
         </is>
       </c>
       <c r="J89" s="17" t="inlineStr">
         <is>
-          <t>Mechanical fix; one-line per function. The discovery helper _discover_apify_actors is single-threaded at startup, so it can keep using _SESSION.</t>
+          <t>All five _SESSION.post(...) call sites swapped to _session().post(...) (mechanical PowerShell -replace). The single-threaded _discover_apify_actors still uses _SESSION.get because it only runs once at startup. Verified grep _SESSION\. returns just that one site.</t>
         </is>
       </c>
     </row>
@@ -10204,27 +10256,27 @@
       </c>
       <c r="F90" s="17" t="inlineStr">
         <is>
-          <t>search_all_platforms fans 6 scrapers into a ThreadPoolExecutor and waits via as_completed(futures) with no overall deadline. The Apify run-sync-get-dataset-items calls have a 130-second per-request timeout. A single slow Apify actor stalls the entire /api/jobs/search response for 130s, with the user seeing only a spinning loader.</t>
-        </is>
-      </c>
-      <c r="G90" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>search_all_platforms fanned 6 scrapers into a ThreadPoolExecutor and waited via as_completed(futures) with no overall deadline. The Apify run-sync-get-dataset-items calls have a 130-second per-request timeout, so a single slow Apify actor stalled the entire /api/jobs/search response for 130s.</t>
+        </is>
+      </c>
+      <c r="G90" s="20" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H90" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Rajesh</t>
         </is>
       </c>
       <c r="I90" s="17" t="inlineStr">
         <is>
-          <t>Wrap as_completed in a budget — e.g. for fut in as_completed(futures, timeout=45): … and treat unfinished futures as failed sources (cancel + log). Surface a partial-results banner in the UI when sources timed out.</t>
+          <t>None (already met).</t>
         </is>
       </c>
       <c r="J90" s="17" t="inlineStr">
         <is>
-          <t>Pairs naturally with a circuit-breaker around Apify (per-actor failure counter that skips the actor for N seconds after K consecutive timeouts).</t>
+          <t>Wrapped as_completed(futures, timeout=60) in a try/except TimeoutError block. When the budget is exceeded we log how many sources were abandoned, cancel pending futures, and return whatever results came back — partial-results UX over a hung spinner.</t>
         </is>
       </c>
     </row>
@@ -10360,27 +10412,27 @@
       </c>
       <c r="F93" s="17" t="inlineStr">
         <is>
-          <t>create_user(email, password) does no validation at the DB layer — it lower()s the email and inserts whatever is provided. All format/length/strength enforcement happens in jobpilot/routes/auth.py; any other future caller (admin script, batch import, future API) bypasses the checks.</t>
-        </is>
-      </c>
-      <c r="G93" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>create_user(email, password) did no validation at the DB layer — it lower()d the email and inserted whatever was provided. Any future caller (admin script, batch import, future API) bypassed the route-layer checks.</t>
+        </is>
+      </c>
+      <c r="G93" s="20" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H93" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Rajesh</t>
         </is>
       </c>
       <c r="I93" s="17" t="inlineStr">
         <is>
-          <t>Add minimal defense-in-depth in create_user: regex on email shape, len(password) &gt;= 8 (or read from env), and reject obviously invalid inputs with ValueError. Do *not* duplicate the route-layer messages — those stay user-facing; this is the safety net.</t>
+          <t>None (already met).</t>
         </is>
       </c>
       <c r="J93" s="17" t="inlineStr">
         <is>
-          <t>Pairs naturally with #2 (input validation) once that work starts.</t>
+          <t>Added defense-in-depth at the DB layer: regex on email shape (_EMAIL_RE_DB), 254-char length cap, len(password) &gt;= 6 check; both raise ValueError with neutral messages so the safety net stays distinct from the user-facing route messages.</t>
         </is>
       </c>
     </row>
@@ -10412,27 +10464,27 @@
       </c>
       <c r="F94" s="17" t="inlineStr">
         <is>
-          <t>_get_apify_actor_ids() makes a live HTTP call to api.apify.com/v2/acts on first invocation. _APIFY_ACTORS_CACHE is populated only on success — there is no negative cache, so every job search during an Apify outage re-issues the discovery call (and pays its full 30s timeout).</t>
-        </is>
-      </c>
-      <c r="G94" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>_get_apify_actor_ids() made a live HTTP call to api.apify.com/v2/acts on first invocation. _APIFY_ACTORS_CACHE was populated only on success — there was no negative cache, so every job search during an Apify outage re-issued the discovery call (and paid its full 30s timeout).</t>
+        </is>
+      </c>
+      <c r="G94" s="20" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H94" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Rajesh</t>
         </is>
       </c>
       <c r="I94" s="17" t="inlineStr">
         <is>
-          <t>Cache *both* success and failure for at least 5 minutes. Even a _APIFY_ACTORS_CACHE = DEFAULT_APIFY_ACTORS.copy() populated on failure (timestamped) would prevent the per-request retry storm.</t>
+          <t>None (already met).</t>
         </is>
       </c>
       <c r="J94" s="17" t="inlineStr">
         <is>
-          <t>Symptom appears as "every search is suddenly slow" — hard to diagnose without log scraping.</t>
+          <t>get_apify_actors() now caches both success *and* failure for 5 min (_APIFY_ACTORS_CACHE_TTL_SEC = 300). On exception we fall back to DEFAULT_APIFY_ACTORS.copy() and stamp the timestamp so the next 300s of searches don't re-hit Apify.</t>
         </is>
       </c>
     </row>
@@ -10464,27 +10516,27 @@
       </c>
       <c r="F95" s="17" t="inlineStr">
         <is>
-          <t>read_resume(filename) builds the path as RESUMES_DIR / filename with no traversal sanitization. If any future caller passes a user-controlled filename containing .., the function will read arbitrary files inside the container. The route layer (jobpilot/routes/resume.py) currently sanitizes, but the helper is a footgun for any new caller.</t>
-        </is>
-      </c>
-      <c r="G95" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>read_resume(filename) built the path as RESUMES_DIR / filename with no traversal sanitization. If any future caller passed a user-controlled filename containing .., the function would read arbitrary files inside the container.</t>
+        </is>
+      </c>
+      <c r="G95" s="20" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H95" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Rajesh</t>
         </is>
       </c>
       <c r="I95" s="17" t="inlineStr">
         <is>
-          <t>Reuse the existing _safe_stem() helper at the top of read_resume (or a parallel _safe_in_path()) and reject anything that resolves outside RESUMES_DIR. Mirror the pattern in _safe_out_path (resolve + startswith check).</t>
+          <t>None (already met).</t>
         </is>
       </c>
       <c r="J95" s="17" t="inlineStr">
         <is>
-          <t>Defense-in-depth — same hardening shape as #67/#65.</t>
+          <t>Added a defense-in-depth guard at the top of read_resume: rejects path separators / .., requires os.path.basename(filename) == filename, and resolves under RESUMES_DIR with a startswith check. Verified empirically (read_resume('../app.py') returns '').</t>
         </is>
       </c>
     </row>
@@ -10516,27 +10568,27 @@
       </c>
       <c r="F96" s="17" t="inlineStr">
         <is>
-          <t>Dead-code typo: parts = after_later = after_label.split("✅ Change Log:", 1). The variable after_later is never read again — looks like a misspelling of after_label that the author meant to drop. Confusing on review and trips static analysis.</t>
-        </is>
-      </c>
-      <c r="G96" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>Dead-code typo: parts = after_later = after_label.split("✅ Change Log:", 1). The variable after_later was never read again.</t>
+        </is>
+      </c>
+      <c r="G96" s="20" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H96" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Rajesh</t>
         </is>
       </c>
       <c r="I96" s="17" t="inlineStr">
         <is>
-          <t>Delete the after_later = chained assignment so the line reads parts = after_label.split("✅ Change Log:", 1).</t>
+          <t>None (already met).</t>
         </is>
       </c>
       <c r="J96" s="17" t="inlineStr">
         <is>
-          <t>Pure cleanup; no behavior change.</t>
+          <t>Dropped the chained assignment; line now reads parts = after_label.split("✅ Change Log:", 1). No behavior change.</t>
         </is>
       </c>
     </row>
@@ -10568,27 +10620,27 @@
       </c>
       <c r="F97" s="17" t="inlineStr">
         <is>
-          <t>_get() always sleeps random.uniform(0.2, 0.6) before issuing the request, even when called from concurrent worker threads in search_all_platforms. With ~6 sources × up to 4 paginated requests each, this adds ~5–15 seconds of pure sleep per search wall-clock budget.</t>
-        </is>
-      </c>
-      <c r="G97" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>_get() always slept random.uniform(0.2, 0.6) before issuing the request, even when called from concurrent worker threads. With ~6 sources × up to 4 paginated requests each, this added ~5–15 seconds of pure sleep per search wall-clock budget.</t>
+        </is>
+      </c>
+      <c r="G97" s="20" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H97" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Rajesh</t>
         </is>
       </c>
       <c r="I97" s="17" t="inlineStr">
         <is>
-          <t>Drop the unconditional sleep. If rate-limit jitter is needed, gate it per-host (only the slow sources — Adzuna and JSearch) and give it a tighter upper bound (≤200 ms).</t>
+          <t>None (already met).</t>
         </is>
       </c>
       <c r="J97" s="17" t="inlineStr">
         <is>
-          <t>Easy win for perceived search speed.</t>
+          <t>Sleep is now gated on the URL touching a known slow / rate-limited host (adzuna.com, jsearch.p.rapidapi.com) and the upper bound is dropped to 0.2s. Free providers (Muse, Remotive, USAJobs, Arbeitnow) skip the sleep entirely — perceived search speed improves significantly.</t>
         </is>
       </c>
     </row>
@@ -10672,27 +10724,27 @@
       </c>
       <c r="F99" s="17" t="inlineStr">
         <is>
-          <t>decode_token() does payload["sub"] directly, raising KeyError if a JWT was signed with our secret but lacks the sub claim. The function's docstring promises only jwt.PyJWTError on failure, so callers who narrow their except will crash with an unhandled KeyError.</t>
-        </is>
-      </c>
-      <c r="G99" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t>decode_token() did payload["sub"] directly, raising KeyError if a JWT was signed with our secret but lacked the sub claim. The function's docstring promised only jwt.PyJWTError on failure, so callers narrowing on except jwt.PyJWTError would crash on the unhandled KeyError.</t>
+        </is>
+      </c>
+      <c r="G99" s="20" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H99" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Rajesh</t>
         </is>
       </c>
       <c r="I99" s="17" t="inlineStr">
         <is>
-          <t>Use payload.get("sub") and raise jwt.InvalidTokenError("sub claim missing") if None. Update the docstring or add a regression test.</t>
+          <t>None (already met).</t>
         </is>
       </c>
       <c r="J99" s="17" t="inlineStr">
         <is>
-          <t>Pure contract bug; trivial fix.</t>
+          <t>Now uses payload.get("sub") and raises jwt.InvalidTokenError("sub claim missing") (a PyJWTError subclass) when missing. Docstring updated. Verified empirically with a no-sub token.</t>
         </is>
       </c>
     </row>
@@ -10797,6 +10849,58 @@
       <c r="J101" s="17" t="inlineStr">
         <is>
           <t>Closes the rest of #67's deduplication intent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="15" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="B102" s="19" t="inlineStr">
+        <is>
+          <t>🟡</t>
+        </is>
+      </c>
+      <c r="C102" s="19" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D102" s="17" t="inlineStr">
+        <is>
+          <t>15. Core/ Backend Audit (added 2026-05-05)</t>
+        </is>
+      </c>
+      <c r="E102" s="17" t="inlineStr">
+        <is>
+          <t>jobpilot/core/job_scraper.py</t>
+        </is>
+      </c>
+      <c r="F102" s="17" t="inlineStr">
+        <is>
+          <t>_title_matches() returned True whenever filler-stripping reduced the alias to zero meaningful tokens (e.g. "team lead" → []). Because search_all_platforms ORs aliases together with any(...), a single such alias acted as a wildcard and let every job from every source pass the title filter. Same class of bug for over-stripped aliases that collapsed to a single generic token (e.g. "tech lead" → ["tech"] matching "Marketing Tech Specialist" for an "engineering manager" search).</t>
+        </is>
+      </c>
+      <c r="G102" s="20" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H102" s="15" t="inlineStr">
+        <is>
+          <t>Rajesh</t>
+        </is>
+      </c>
+      <c r="I102" s="17" t="inlineStr">
+        <is>
+          <t>None (already met).</t>
+        </is>
+      </c>
+      <c r="J102" s="17" t="inlineStr">
+        <is>
+          <t>Filter is now fail-closed: empty query_words returns False, and aliases whose original token count was ≥ 2 must keep ≥ 2 meaningful tokens after filler-stripping (otherwise the alias is too noisy and is rejected). Verified with a 11-case smoke matrix; existing 5/5 pytest suite still green.</t>
         </is>
       </c>
     </row>
@@ -10912,7 +11016,7 @@
         <v>7</v>
       </c>
       <c r="D4" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="15" t="n">
         <v>0</v>
@@ -10921,7 +11025,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -10936,10 +11040,10 @@
         </is>
       </c>
       <c r="C5" s="15" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D5" s="15" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="E5" s="15" t="n">
         <v>9</v>
@@ -10948,7 +11052,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -10966,7 +11070,7 @@
         <v>38</v>
       </c>
       <c r="D6" s="15" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E6" s="15" t="n">
         <v>2</v>
@@ -10975,7 +11079,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -10985,10 +11089,10 @@
         </is>
       </c>
       <c r="C7" s="23" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D7" s="23" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="E7" s="23" t="n">
         <v>11</v>
@@ -10997,7 +11101,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="23" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
@@ -11026,7 +11130,7 @@
         </is>
       </c>
       <c r="B12" s="15" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -11046,7 +11150,7 @@
         </is>
       </c>
       <c r="B14" s="15" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15">
@@ -11111,13 +11215,13 @@
         <v>1</v>
       </c>
       <c r="D20" s="15" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="E20" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F20" s="15" t="n">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21">
@@ -11127,7 +11231,7 @@
         </is>
       </c>
       <c r="B21" s="15" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C21" s="15" t="n">
         <v>0</v>
@@ -11139,7 +11243,7 @@
         <v>11</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -11153,7 +11257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11644,6 +11748,141 @@
         </is>
       </c>
       <c r="E18" s="17" t="inlineStr">
+        <is>
+          <t>Rajesh</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>**ATS / scraping / CI sprint.** Three focused fixes per user request. (1) CLAUDE_MODEL default flipped from the bogus claude-sonnet-4-6 to the stable claude-sonnet-4-5 alias — score_ats and every other Claude-backed call now succeed when the env var is unset, and .env.example is updated in lockstep. (2) New issue #101: _title_matches() was wildcard-passing every job whenever an alias filler-stripped to zero meaningful tokens (e.g. "team lead" → []) or to a single over-generic token (e.g. "tech lead" → ["tech"]); filter is now fail-closed and rejects over-stripped aliases. (3) CI workflow now injects ANTHROPIC_API_KEY from secrets.ANTHROPIC_API_KEY so future Claude-touching tests can reach the API. Smoke tests still 5/5 green; verified the new title filter against an 11-case matrix.</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>#84, #101 (new)</t>
+        </is>
+      </c>
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t>jobpilot/core/ai_engine.py, jobpilot/core/job_scraper.py, jobpilot/.env.example, .github/workflows/ci.yml</t>
+        </is>
+      </c>
+      <c r="E19" s="17" t="inlineStr">
+        <is>
+          <t>Rajesh</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>**Section 15 sweep — safe trivial/medium remediation.** Closed 9 of the Section 15 findings the AGENTS.md §4 deferral list permits. Backend hardening: _SEARCH_CACHE now self-evicts (TTL + cap of 128); all five search_apify_* swapped from module-level _SESSION.post to per-thread _session().post (closes #25 regression); search_all_platforms enforces a 60-second wall-clock budget via as_completed(timeout=…) and cancels stragglers; get_apify_actors() negatively caches outage failures for 5 min so search throughput doesn't collapse during Apify incidents; _get() only sleeps for slow rate-limited hosts (Adzuna / JSearch) instead of taxing every request. Auth/security: create_user() validates email shape (regex + 254-char cap) and minimum password length at the DB layer; decode_token() raises jwt.InvalidTokenError instead of leaking KeyError when the sub claim is missing; read_resume() rejects path-traversal filenames (verified '../app.py' returns ''). Cleanup: dropped dead after_later = chained assignment in apply_chat_instruction. Pytest 5/5 green; functional smoke of every new guard verified. **Explicitly skipped per AGENTS.md §4:** #1, #2, #3, #4, #9, #17, #20, #85, #86, #90, #91, #97, #99, #100 (reserved for the deliberate critical/high security sprint with tests).</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>#87, #88, #89, #92, #93, #94, #95, #96, #98</t>
+        </is>
+      </c>
+      <c r="D20" s="17" t="inlineStr">
+        <is>
+          <t>jobpilot/core/ai_engine.py, jobpilot/core/job_scraper.py, jobpilot/core/auth_db.py, jobpilot/core/resume_reader.py</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
+        <is>
+          <t>Rajesh</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>**Canonical domain + GitHub Sign-In.** Per user request: https://www.jobspilot.site is now the single canonical URL across the app and docs. Replaced every jobpilot-production-1eb8.up.railway.app reference in README.md, AGENTS.md, and the landing hero with www.jobspilot.site; dropped the "Coming soon" pill (the domain is live now). Added GitHub OAuth (Authorization Code grant) so JobPilot can be hosted as a GitHub OAuth App: new /api/auth/github/start and /api/auth/github/callback routes in jobpilot/routes/auth.py with secrets.compare_digest CSRF state in the Flask session, server-side code/token exchange via requests, and a small bootstrap HTML page that mirrors setLoginSession()'s localStorage shape so the JWT lands the user on /app exactly like the email and Google paths. Landing modal now shows a **Continue with GitHub** button gated on both GITHUB_CLIENT_ID and GITHUB_CLIENT_SECRET (with a ?debug=1 not-configured hint matching the Google pattern); the "or continue with" divider auto-shows when *either* OAuth provider is configured. New env vars (GITHUB_CLIENT_ID, GITHUB_CLIENT_SECRET, optional GITHUB_REDIRECT_URI) added to jobpilot/.env.example and README.md, with a step-by-step **Enable GitHub Sign-In** section. Pytest 5/5 still green.</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>New feature (no prior issue ID)</t>
+        </is>
+      </c>
+      <c r="D21" s="17" t="inlineStr">
+        <is>
+          <t>README.md, AGENTS.md, jobpilot/app.py, jobpilot/routes/auth.py, jobpilot/templates/landing.html, jobpilot/.env.example</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="inlineStr">
+        <is>
+          <t>Rajesh</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>**Resume-first onboarding flow.** Per user request: after sign-in, the app now shows a single welcome modal asking the user to upload their resume *once* (large "Upload Resume" CTA → existing POST /api/upload-resume → text+filename persisted to localStorage under jp_resume_text / jp_resume_name). On success the modal closes, a toast confirms the save, and the sidebar search button is reframed as **"Start Job Scraping"** with a 3-pulse teal halo + autoscroll/focus to draw attention. The pre-uploaded resume is reused for every job: openJob() pre-loads state.resumeText / state.resumeName from the global store, and the Tailor tab's idle state now renders a one-click *"Tailor Resume for this Job"* button (instead of forcing the user back through the upload picker) plus a discreet *"Use a different resume"* link. resetTailor() keeps the stored resume in place. logout() clears jp_resume_text / jp_resume_name alongside the JWT so account switches don't leak resume text. Added a small &lt;style&gt; block in jobpilot/templates/index.html for the welcome overlay + scrape-ready pulse so jobpilot/static/css/style.css stays untouched (per AGENTS.md §2.8). Pytest 5/5 still green.</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>New feature (no prior issue ID)</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="inlineStr">
+        <is>
+          <t>jobpilot/templates/index.html, jobpilot/static/js/app.js</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="inlineStr">
+        <is>
+          <t>Rajesh</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>**MVP foundation sprint.** Implemented the 7-item MVP shortlist on top of the resume-first flow. (1) **Server-side resume persistence** — extended jobpilot/core/auth_db.py with idempotent ALTER TABLE migrations adding resume_text / resume_name / resume_updated columns plus save_user_resume, get_user_resume, clear_user_resume, delete_user helpers (text capped at RESUME_TEXT_MAX_CHARS = 200K). _auth_guard in jobpilot/app.py now stores the decoded email in flask.g.email; /api/upload-resume persists best-effort to the DB; new GET/DELETE /api/me/resume and DELETE /api/me routes in jobpilot/routes/auth.py (demo account cannot self-delete). Frontend initApp() now hydrates the resume from /api/me/resume so a fresh device or cleared cache still recovers it. (2) **Per-user Anthropic rate-limit** — sliding 24h window in app.py (RATE_LIMIT_PER_USER = 60/day, RATE_LIMIT_DEMO = 10/day) over /api/tailor, /api/score, /api/chat-instruction, /api/improve-line, /api/generate-resume, /api/suggest-certs, /api/answer. Returns 429 {detail, used, cap}. Partial mitigation for #22 (in-memory only — Postgres migration #23 still required for fleet-wide enforcement). (3) **Topbar resume chip** — persistent 📄 filename · Replace · × chip (rendered by renderTopbarResumeChip()) so the user always knows what the AI will tailor against; "Replace" reuses the welcome-modal file picker, "×" calls DELETE /api/me/resume. (4) **Smart welcome trigger + drag-and-drop** — modal only re-shows if no resume on file *and* jp_welcome_seen not in sessionStorage; the modal card now accepts file drops with a teal dashed drop-active outline. (5) **Privacy + Terms** — already pre-existed in jobpilot/app.py (no change required). (6) **Account self-delete** — deleteMyAccount() in jobpilot/static/js/app.js calls DELETE /api/me after a hard confirm dialog, then logout({silent:true}). (7) **Production secret fail-fast** — create_app() refuses to boot when FLASK_ENV=production (or RAILWAY_ENVIRONMENT set) if FLASK_SECRET or JWT_SECRET is the placeholder default or shorter than 32 chars; partial mitigation for §4 secret-hardening sprint. New CSS appended to jobpilot/static/css/style.css for the chip / drop-zone / pulse styles. Pytest still 5/5 green.</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>New feature + partial #22, partial §4 secret hardening</t>
+        </is>
+      </c>
+      <c r="D23" s="17" t="inlineStr">
+        <is>
+          <t>jobpilot/core/auth_db.py, jobpilot/app.py, jobpilot/routes/auth.py, jobpilot/routes/resume.py, jobpilot/static/js/app.js, jobpilot/static/css/style.css</t>
+        </is>
+      </c>
+      <c r="E23" s="17" t="inlineStr">
         <is>
           <t>Rajesh</t>
         </is>

--- a/REPO_ISSUES_REPORT.xlsx
+++ b/REPO_ISSUES_REPORT.xlsx
@@ -277,8 +277,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AllIssues" displayName="AllIssues" ref="A1:J102" headerRowCount="1">
-  <autoFilter ref="A1:J102"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AllIssues" displayName="AllIssues" ref="A1:J103" headerRowCount="1">
+  <autoFilter ref="A1:J103"/>
   <tableColumns count="10">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Pri"/>
@@ -448,8 +448,8 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="Sec17" displayName="Sec17" ref="A2:J20" headerRowCount="1">
-  <autoFilter ref="A2:J20"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="Sec17" displayName="Sec17" ref="A2:J21" headerRowCount="1">
+  <autoFilter ref="A2:J21"/>
   <tableColumns count="10">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Pri"/>
@@ -467,8 +467,8 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="ChangeLog" displayName="ChangeLog" ref="A1:E23" headerRowCount="1">
-  <autoFilter ref="A1:E23"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="ChangeLog" displayName="ChangeLog" ref="A1:E29" headerRowCount="1">
+  <autoFilter ref="A1:E29"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Date"/>
     <tableColumn id="2" name="Change"/>
@@ -3610,19 +3610,19 @@
           <t>sessionHistory is a top-level mutable global.</t>
         </is>
       </c>
-      <c r="G3" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="G3" s="20" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H3" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Rajesh</t>
         </is>
       </c>
       <c r="I3" s="17" t="inlineStr">
         <is>
-          <t>Wrap app.js in an IIFE or convert to ES modules (needs build tool, see #44/#45); confirm no other globals depend on window.sessionHistory.</t>
+          <t>Switched the two lets to idempotent var declarations backed by window.sessionHistory / window._sessionHistoryOpen, and rewired clearSessionHistory() and the logout reset to mutate the array in place (length = 0) so any aliasing binding stays valid. A second &lt;script&gt; include of app.js no longer throws a redeclaration error or wipes the in-progress activity log. Full IIFE/module wrapper is intentionally deferred until a bundler lands (see #44 / #45).</t>
         </is>
       </c>
       <c r="J3" s="17" t="inlineStr">
@@ -4558,7 +4558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="E9" s="17" t="inlineStr">
         <is>
-          <t>jobpilot/core/ai_engine.py, jobpilot/core/ai_engine.py, jobpilot/core/ai_engine.py</t>
+          <t>jobpilot/core/ai_engine.py, jobpilot/core/ai_engine.py, jobpilot/core/ai_engine.py, jobpilot/core/ai_engine.py</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr">
@@ -4975,19 +4975,19 @@
           <t>tailor_resume, apply_chat_instruction, generate_resume, and answer_screening_question all silently truncate inputs (resume_text[:6000], job_description[:3000], description[:2000], etc.) without surfacing any warning to the caller. Only score_ats reports truncation_warning. Long resumes / JDs lose tail content (often the most recent role) with no user feedback.</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Rajesh</t>
         </is>
       </c>
       <c r="I9" s="17" t="inlineStr">
         <is>
-          <t>Promote the truncation_warning pattern from score_ats into a shared helper, return it in every result dict, and surface a small banner in the UI when present. Limits should remain env-overridable (existing pattern).</t>
+          <t>Promoted the score_ats truncation pattern into shared helpers (_truncate, _format_truncation_warning). All five Claude-bound functions now route every clipped field through the helper and surface a single truncation_warning in their result dicts (generate_resume and answer_screening_question were widened from str to dict for this). Routes (/api/tailor, /api/chat-instruction, /api/generate-resume, /api/score, /api/answer) forward the field, and the frontend toast helper notifyTruncation() raises a soft warning to the user when present. Limits are unchanged so cost/latency behavior is identical.</t>
         </is>
       </c>
       <c r="J9" s="17" t="inlineStr">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="E10" s="17" t="inlineStr">
         <is>
-          <t>jobpilot/core/resume_reader.py</t>
+          <t>jobpilot/core/resume_reader.py, jobpilot/routes/resume.py, jobpilot/static/js/app.js</t>
         </is>
       </c>
       <c r="F10" s="17" t="inlineStr">
@@ -5027,19 +5027,19 @@
           <t>save_tailored_pdf swallows every WeasyPrint exception and silently falls back to the ReportLab path. The two paths produce visibly different PDFs (different fonts, spacing, no teal accent). End-users hitting a WeasyPrint misconfig (missing system libs, font failure) get a degraded PDF with no notice and no trail beyond a logger.warning.</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H10" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Rajesh</t>
         </is>
       </c>
       <c r="I10" s="17" t="inlineStr">
         <is>
-          <t>Either (a) propagate the WeasyPrint failure to the route layer and return a 502 with a clear message, or (b) include a one-line note in the response payload (pdf_renderer: "reportlab-fallback") and surface it in the UI when downloading. Add a smoke test that asserts WeasyPrint actually ran in the happy path.</t>
+          <t>save_tailored_pdf now returns (path, renderer) where renderer is "weasyprint" or "reportlab". The /api/download route stamps that into an X-PDF-Renderer response header, and downloadResume() raises a destructive-style toast when it sees the reportlab value so the user knows styling may differ from the preview. The existing logger.warning path that pinpointed the WeasyPrint failure cause is preserved.</t>
         </is>
       </c>
       <c r="J10" s="17" t="inlineStr">
@@ -5565,6 +5565,58 @@
       <c r="J20" s="17" t="inlineStr">
         <is>
           <t>Filter is now fail-closed: empty query_words returns False, and aliases whose original token count was ≥ 2 must keep ≥ 2 meaningful tokens after filler-stripping (otherwise the alias is too noisy and is rejected). Verified with a 11-case smoke matrix; existing 5/5 pytest suite still green.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>🟠</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D21" s="17" t="inlineStr">
+        <is>
+          <t>15. Core/ Backend Audit (added 2026-05-05)</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="inlineStr">
+        <is>
+          <t>jobpilot/core/job_scraper.py</t>
+        </is>
+      </c>
+      <c r="F21" s="17" t="inlineStr">
+        <is>
+          <t>Sidebar filters (Location, Date posted, Seniority) silently leaked unrelated jobs into the results: (a) _is_us_or_remote() had a "short string ≤ 3 words → keep" fallback that let single-word foreign cities like "Berlin", "Munich", "London" pass even when the user explicitly searched within the United States; (b) search_usajobs hard-coded DatePosted: 1 and ignored the date_posted parameter entirely; (c) The Muse / Remotive / Arbeitnow have no server-side date filter at all, so jobs posted weeks ago appeared under "Last 24 hours".</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H21" s="15" t="inlineStr">
+        <is>
+          <t>Rajesh</t>
+        </is>
+      </c>
+      <c r="I21" s="17" t="inlineStr">
+        <is>
+          <t>None (already met).</t>
+        </is>
+      </c>
+      <c r="J21" s="17" t="inlineStr">
+        <is>
+          <t>Three-part fix: (1) added a _FOREIGN_CITIES whole-word blocklist (~100 cities across Europe / Asia / Pacific / MENA / Americas) and expanded _NON_US_COUNTRIES so the location filter now rejects Berlin / Munich / Bangalore, India etc. while still accepting Newark, NJ (substring would otherwise match) and Seattle, WA. (2) Threaded the date_posted argument into search_usajobs and mapped past24Hours/pastWeek/pastMonth → 1/7/30 for the USAJobs DatePosted param. (3) Added a _days_old() parser and a new post-filter step in search_all_platforms that drops jobs older than the user-requested window (with fail-open semantics on unparseable dates so format drift in any single source doesn't blank the result set). Smoke-verified all 9 location cases + 6 date cases; pytest still 5/5 green.</t>
         </is>
       </c>
     </row>
@@ -5585,7 +5637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J102"/>
+  <dimension ref="A1:J103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -9219,19 +9271,19 @@
           <t>sessionHistory is a top-level mutable global.</t>
         </is>
       </c>
-      <c r="G70" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="G70" s="20" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H70" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Rajesh</t>
         </is>
       </c>
       <c r="I70" s="17" t="inlineStr">
         <is>
-          <t>Wrap app.js in an IIFE or convert to ES modules (needs build tool, see #44/#45); confirm no other globals depend on window.sessionHistory.</t>
+          <t>Switched the two lets to idempotent var declarations backed by window.sessionHistory / window._sessionHistoryOpen, and rewired clearSessionHistory() and the logout reset to mutate the array in place (length = 0) so any aliasing binding stays valid. A second &lt;script&gt; include of app.js no longer throws a redeclaration error or wipes the in-progress activity log. Full IIFE/module wrapper is intentionally deferred until a bundler lands (see #44 / #45).</t>
         </is>
       </c>
       <c r="J70" s="17" t="inlineStr">
@@ -10303,7 +10355,7 @@
       </c>
       <c r="E91" s="17" t="inlineStr">
         <is>
-          <t>jobpilot/core/ai_engine.py, jobpilot/core/ai_engine.py, jobpilot/core/ai_engine.py</t>
+          <t>jobpilot/core/ai_engine.py, jobpilot/core/ai_engine.py, jobpilot/core/ai_engine.py, jobpilot/core/ai_engine.py</t>
         </is>
       </c>
       <c r="F91" s="17" t="inlineStr">
@@ -10311,19 +10363,19 @@
           <t>tailor_resume, apply_chat_instruction, generate_resume, and answer_screening_question all silently truncate inputs (resume_text[:6000], job_description[:3000], description[:2000], etc.) without surfacing any warning to the caller. Only score_ats reports truncation_warning. Long resumes / JDs lose tail content (often the most recent role) with no user feedback.</t>
         </is>
       </c>
-      <c r="G91" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="G91" s="20" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H91" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Rajesh</t>
         </is>
       </c>
       <c r="I91" s="17" t="inlineStr">
         <is>
-          <t>Promote the truncation_warning pattern from score_ats into a shared helper, return it in every result dict, and surface a small banner in the UI when present. Limits should remain env-overridable (existing pattern).</t>
+          <t>Promoted the score_ats truncation pattern into shared helpers (_truncate, _format_truncation_warning). All five Claude-bound functions now route every clipped field through the helper and surface a single truncation_warning in their result dicts (generate_resume and answer_screening_question were widened from str to dict for this). Routes (/api/tailor, /api/chat-instruction, /api/generate-resume, /api/score, /api/answer) forward the field, and the frontend toast helper notifyTruncation() raises a soft warning to the user when present. Limits are unchanged so cost/latency behavior is identical.</t>
         </is>
       </c>
       <c r="J91" s="17" t="inlineStr">
@@ -10355,7 +10407,7 @@
       </c>
       <c r="E92" s="17" t="inlineStr">
         <is>
-          <t>jobpilot/core/resume_reader.py</t>
+          <t>jobpilot/core/resume_reader.py, jobpilot/routes/resume.py, jobpilot/static/js/app.js</t>
         </is>
       </c>
       <c r="F92" s="17" t="inlineStr">
@@ -10363,19 +10415,19 @@
           <t>save_tailored_pdf swallows every WeasyPrint exception and silently falls back to the ReportLab path. The two paths produce visibly different PDFs (different fonts, spacing, no teal accent). End-users hitting a WeasyPrint misconfig (missing system libs, font failure) get a degraded PDF with no notice and no trail beyond a logger.warning.</t>
         </is>
       </c>
-      <c r="G92" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="G92" s="20" t="inlineStr">
+        <is>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="H92" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Rajesh</t>
         </is>
       </c>
       <c r="I92" s="17" t="inlineStr">
         <is>
-          <t>Either (a) propagate the WeasyPrint failure to the route layer and return a 502 with a clear message, or (b) include a one-line note in the response payload (pdf_renderer: "reportlab-fallback") and surface it in the UI when downloading. Add a smoke test that asserts WeasyPrint actually ran in the happy path.</t>
+          <t>save_tailored_pdf now returns (path, renderer) where renderer is "weasyprint" or "reportlab". The /api/download route stamps that into an X-PDF-Renderer response header, and downloadResume() raises a destructive-style toast when it sees the reportlab value so the user knows styling may differ from the preview. The existing logger.warning path that pinpointed the WeasyPrint failure cause is preserved.</t>
         </is>
       </c>
       <c r="J92" s="17" t="inlineStr">
@@ -10901,6 +10953,58 @@
       <c r="J102" s="17" t="inlineStr">
         <is>
           <t>Filter is now fail-closed: empty query_words returns False, and aliases whose original token count was ≥ 2 must keep ≥ 2 meaningful tokens after filler-stripping (otherwise the alias is too noisy and is rejected). Verified with a 11-case smoke matrix; existing 5/5 pytest suite still green.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="15" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="B103" s="18" t="inlineStr">
+        <is>
+          <t>🟠</t>
+        </is>
+      </c>
+      <c r="C103" s="18" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D103" s="17" t="inlineStr">
+        <is>
+          <t>15. Core/ Backend Audit (added 2026-05-05)</t>
+        </is>
+      </c>
+      <c r="E103" s="17" t="inlineStr">
+        <is>
+          <t>jobpilot/core/job_scraper.py</t>
+        </is>
+      </c>
+      <c r="F103" s="17" t="inlineStr">
+        <is>
+          <t>Sidebar filters (Location, Date posted, Seniority) silently leaked unrelated jobs into the results: (a) _is_us_or_remote() had a "short string ≤ 3 words → keep" fallback that let single-word foreign cities like "Berlin", "Munich", "London" pass even when the user explicitly searched within the United States; (b) search_usajobs hard-coded DatePosted: 1 and ignored the date_posted parameter entirely; (c) The Muse / Remotive / Arbeitnow have no server-side date filter at all, so jobs posted weeks ago appeared under "Last 24 hours".</t>
+        </is>
+      </c>
+      <c r="G103" s="20" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="H103" s="15" t="inlineStr">
+        <is>
+          <t>Rajesh</t>
+        </is>
+      </c>
+      <c r="I103" s="17" t="inlineStr">
+        <is>
+          <t>None (already met).</t>
+        </is>
+      </c>
+      <c r="J103" s="17" t="inlineStr">
+        <is>
+          <t>Three-part fix: (1) added a _FOREIGN_CITIES whole-word blocklist (~100 cities across Europe / Asia / Pacific / MENA / Americas) and expanded _NON_US_COUNTRIES so the location filter now rejects Berlin / Munich / Bangalore, India etc. while still accepting Newark, NJ (substring would otherwise match) and Seattle, WA. (2) Threaded the date_posted argument into search_usajobs and mapped past24Hours/pastWeek/pastMonth → 1/7/30 for the USAJobs DatePosted param. (3) Added a _days_old() parser and a new post-filter step in search_all_platforms that drops jobs older than the user-requested window (with fail-open semantics on unparseable dates so format drift in any single source doesn't blank the result set). Smoke-verified all 9 location cases + 6 date cases; pytest still 5/5 green.</t>
         </is>
       </c>
     </row>
@@ -11013,10 +11117,10 @@
         </is>
       </c>
       <c r="C4" s="15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" s="15" t="n">
         <v>0</v>
@@ -11043,7 +11147,7 @@
         <v>51</v>
       </c>
       <c r="D5" s="15" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E5" s="15" t="n">
         <v>9</v>
@@ -11052,7 +11156,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -11089,10 +11193,10 @@
         </is>
       </c>
       <c r="C7" s="23" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D7" s="23" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E7" s="23" t="n">
         <v>11</v>
@@ -11101,7 +11205,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="23" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
@@ -11130,7 +11234,7 @@
         </is>
       </c>
       <c r="B12" s="15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -11150,7 +11254,7 @@
         </is>
       </c>
       <c r="B14" s="15" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15">
@@ -11215,13 +11319,13 @@
         <v>1</v>
       </c>
       <c r="D20" s="15" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E20" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F20" s="15" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21">
@@ -11231,7 +11335,7 @@
         </is>
       </c>
       <c r="B21" s="15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C21" s="15" t="n">
         <v>0</v>
@@ -11243,7 +11347,7 @@
         <v>11</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -11257,7 +11361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11885,6 +11989,168 @@
       <c r="E23" s="17" t="inlineStr">
         <is>
           <t>Rajesh</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>**Job-search filter fix sprint (#102).** Reproduced and fixed the user-reported bug that searching with location United States still returned jobs from Berlin / Munich / London, plus latent gaps in the Date-posted and Seniority filters. (a) _is_us_or_remote() short-string fallback was rewritten with a _FOREIGN_CITIES whole-word blocklist (~100 cities across Europe / Asia / Pacific / MENA / Americas) and an expanded _NON_US_COUNTRIES set so Arbeitnow's foreign single-word locations now fail the filter while real US single-word/short-string locations still pass; whole-word matching avoids false positives like Newark containing ark. (b) search_usajobs now accepts and honours the date_posted arg (mapped 1 / 7 / 30 days) — it previously hard-coded DatePosted: 1. (c) Added a new _days_old() parser and a date post-filter in search_all_platforms so The Muse / Remotive / Arbeitnow (which have no server-side date filter) are also bounded by the user-selected window; the post-filter is fail-open on unparseable dates so format drift in any single source can't blank the result set. Smoke-verified all 9 location cases + 6 date cases; pytest still 5/5 green.</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>#102 (new)</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="inlineStr">
+        <is>
+          <t>jobpilot/core/job_scraper.py</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="inlineStr">
+        <is>
+          <t>Rajesh</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>**Medium-Open burndown (#69, #90, #91).** Closed the three remaining 🟡 Medium Open issues in a single minimal-diff sprint. (#69) Frontend sessionHistory / _sessionHistoryOpen switched from let to idempotent var declarations backed by window.*, and clearSessionHistory() / the logout reset now mutate the array in place (sessionHistory.length = 0) instead of reassigning — re-including app.js no longer throws a redeclaration error or wipes the in-progress activity log. Full IIFE/module wrapper still deferred until a bundler (#44 / #45) lands. (#90) Promoted score_ats's truncation_warning pattern into shared _truncate / _format_truncation_warning helpers; tailor_resume, apply_chat_instruction, score_ats, suggest_certifications, generate_resume, and answer_screening_question now all surface a single truncation_warning field. generate_resume / answer_screening_question were widened from str to dict to carry it; routes (/api/tailor, /api/chat-instruction, /api/generate-resume, /api/score, /api/answer) forward it; new frontend notifyTruncation() toast surfaces the warning to the user on every Claude-touching action. Limits unchanged so cost/latency are identical. (#91) save_tailored_pdf now returns (path, renderer) where renderer ∈ {weasyprint, reportlab}; /api/download stamps it into an X-PDF-Renderer response header; downloadResume() raises a destructive-style toast when the WeasyPrint → ReportLab fallback fires so the user knows styling may differ from the preview. The existing logger.warning that pinpoints the WeasyPrint failure cause is preserved. Pytest still 5/5 green.</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>#69, #90, #91</t>
+        </is>
+      </c>
+      <c r="D25" s="17" t="inlineStr">
+        <is>
+          <t>jobpilot/core/ai_engine.py, jobpilot/core/resume_reader.py, jobpilot/routes/resume.py, jobpilot/static/js/app.js</t>
+        </is>
+      </c>
+      <c r="E25" s="17" t="inlineStr">
+        <is>
+          <t>Rajesh</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>**Multi-resume library + topbar Upload.** Per user request: users can now keep multiple named resumes (base + tailored variants) and pick which one is "active" for new searches. Backend: new user_resumes SQLite table created via idempotent init_db() migration with a per-user cap of 20 (env-overridable via RESUME_LIBRARY_MAX); helpers list_user_resumes / add_user_resume / get_user_resume_by_id / delete_user_resume_by_id / set_default_user_resume in jobpilot/core/auth_db.py. The legacy users.resume_* columns now act as the "active pointer" so existing /api/me/resume, /api/upload-resume, and the topbar resume chip continue to work unchanged. save_user_resume() upserts the active resume into the library by name (best-effort), and delete_user_resume_by_id() re-points the active resume to the most-recent remaining entry to avoid leaving the user with a dangling active. Five new auth-guarded endpoints in jobpilot/routes/auth.py: GET /api/me/resumes (metadata + 160-char preview), GET /api/me/resumes/&lt;id&gt; (full text), POST /api/me/resumes (used by the post-tailor save flow), DELETE /api/me/resumes/&lt;id&gt;, POST /api/me/resumes/&lt;id&gt;/default. Frontend: new always-visible **📄 Resumes** topbar button (with badge showing library count) that opens a Library modal listing every saved resume with name + date + size + 2-line preview, source badges (Active / Tailored / Generated / Upload), and per-row [Use this] / [Delete] buttons; the modal also has its own Upload area (reuses /api/upload-resume) so users can add resumes after login. After every successful tailor, a **Save to library** action bar appears under the download buttons; clicking it POSTs the tailored text as Tailored — {Company} — {Title} — {YYYY-MM-DD} so the variant is reusable for the next search. Modal closes on Escape / backdrop click. New CSS lives in jobpilot/templates/index.html (per AGENTS.md §2.8 — no style.css edits). Smoke-tested all DB helpers end-to-end (list / add / set-default / cascade-delete-active); pytest still 5/5 green.</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>New feature (no prior issue ID)</t>
+        </is>
+      </c>
+      <c r="D26" s="17" t="inlineStr">
+        <is>
+          <t>jobpilot/core/auth_db.py, jobpilot/routes/auth.py, jobpilot/templates/index.html, jobpilot/static/js/app.js</t>
+        </is>
+      </c>
+      <c r="E26" s="17" t="inlineStr">
+        <is>
+          <t>Rajesh</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>**Phase 1 — BYOK + Google Drive refactor (backend + frontend).** Per user request, begin transforming JobPilot into a stateless self-hostable BYOK tool. **Identity:** Google Sign-In is now the only identity provider. Removed /api/auth/register, /api/auth/login, /api/auth/github/start, /api/auth/github/callback from jobpilot/routes/auth.py (truncated from 343 to 177 lines). Removed passlib / CryptContext / hash_password / verify_password / create_user / get_user / _EMAIL_RE_DB from jobpilot/core/auth_db.py with a new docstring noting the file will be renamed core/jwt_session.py in Phase 4. Removed the GitHub env-var startup warning + github_enabled template flag from jobpilot/app.py; _PUBLIC_PATHS is now {"/", "/app", "/terms", "/privacy", "/api/auth/google", "/api/auth/demo", "/api/health"}. **Frontend:** jobpilot/templates/landing.html auth modal HTML rewritten — email/password tabs, GitHub button, submitAuth / switchTab / githubSignIn / initGithubSignIn / syncOAuthDividerVisibility all removed; the modal now shows only the Google button + demo button. handleGoogleCredential chains google.accounts.oauth2.initTokenClient({scope:'openid email profile drive.appdata drive.file'}).requestAccessToken({prompt:'consent'}) so a Drive-scoped access_token is captured into localStorage.jp_gtoken (+ jp_gtoken_expiry) BEFORE redirecting to /app — Phase 3 will use it for Drive-backed resume storage with no second consent prompt. enterDemoMode() explicitly wipes any stale jp_gtoken (demo users never get Drive). jobpilot/static/js/app.js gets new helpers getGoogleToken() (silent refresh via requestAccessToken({prompt:''}), returns cached token if not expired with 60s safety buffer) and gAuthHeaders() (adds X-Google-Token header alongside the JWT bearer); clearLoginSession() now wipes jp_gtoken/jp_gtoken_expiry alongside the JWT. The pre-existing switchAuthTab / submitAuth / googleSignIn / handleGoogleCredential stubs in app.js were rewritten as documented no-ops (the real handlers live on landing.html). jobpilot/templates/index.html IIFE expiry-cleanup now also wipes jp_gtoken/jp_gtoken_expiry. **Config:** jobpilot/.env.example — removed GITHUB_CLIENT_ID / GITHUB_CLIENT_SECRET / GITHUB_REDIRECT_URI; added a comment block above GOOGLE_CLIENT_ID listing the required scopes; relabeled ANTHROPIC_API_KEY / RAPIDAPI_KEY / ADZUNA_* as demo-only fallbacks (BYOK arrives in Phase 2). **Tests:** tests/test_auth_smoke.py — replaced test_register_rejects_blank_credentials with test_register_route_removed / test_login_route_removed / test_github_oauth_route_removed (all assert 401 or 404 and verify no token is minted). pytest now 7/7 green. **Docs:** README.md auth section + env-var table rewritten for Google-only sign-in; the entire **Enable GitHub Sign-In** section deleted; the Drive scopes are now documented in the **Enable Google Sign-In** steps; a "Note on removed providers" block flags that GITHUB_* env vars are now safe to delete. **Decisions locked (per user):** GitHub auth removed entirely; demo keeps server-side ANTHROPIC_API_KEY/RAPIDAPI_KEY as fallback with a tighter rate limit; hard cutover (Phase 4 will wipe users.db on deploy); pure client-side Google token via GIS Token Client (no server-side refresh_token). **Next:** Phases 2 (BYOK Settings modal + AES-GCM encryption + X-*-Key header threading), 3 (Drive appDataFolder storage), 4 (drop passlib + rename core/auth_db.py -&gt; core/jwt_session.py), 5 (CSP / header-injection guard / JWT TTL 24h). Pausing here for user review.</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>New feature (no prior issue ID)</t>
+        </is>
+      </c>
+      <c r="D27" s="17" t="inlineStr">
+        <is>
+          <t>jobpilot/app.py, jobpilot/routes/auth.py, jobpilot/core/auth_db.py, jobpilot/templates/landing.html, jobpilot/templates/index.html, jobpilot/static/js/app.js, jobpilot/.env.example, tests/test_auth_smoke.py, README.md</t>
+        </is>
+      </c>
+      <c r="E27" s="17" t="inlineStr">
+        <is>
+          <t>Rajesh</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>**Phase 2A — BYOK backend foundation (Anthropic only; demo-fallback preserved).** Per user request, continued the BYOK + Drive refactor. Real Google-signed-in users must now supply their own Anthropic API key on every Claude-touching request via the X-Anthropic-Key header (optionally X-Claude-Model); the server-side ANTHROPIC_API_KEY env var is preserved as fallback **only for the shared demo account**. **New module:** jobpilot/core/byok.py exposes get_api_key(header, env, *, email, allow_env_for_demo=True) and require_api_key(...) returning a Flask (json, status) error tuple. Both reject keys containing \r / \n / \x00 (header-injection guard, Phase 5 preview). **Refactored:** jobpilot/core/ai_engine.py replaced the single memoised _CLIENT with a per-key _CLIENT_BY_KEY dict so each real user's connection pool is reused without leaking across users. New _resolve_key_and_model() reads flask.g.anthropic_key / flask.g.claude_model (set by the route) and falls back to env vars when there's no Flask context (CLI / pytest / demo). _call() and _client() accept an explicit api_key so the /api/byok/test probe can validate a key *before* it's saved. **Wired:** jobpilot/routes/resume.py added a 14-line _resolve_anthropic() helper called at the top of every Claude route (/api/generate-resume, /api/score, /api/tailor, /api/improve-line, /api/chat-instruction, /api/suggest-certs, /api/answer). Real users with no header get a 400 {detail, byok_required: true, header: 'X-Anthropic-Key'} pointing at Settings; demo users transparently use the env-var fallback. **New blueprint:** jobpilot/routes/byok.py exposes GET /api/byok/test?provider={anthropic</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>jsearch</t>
+        </is>
+      </c>
+      <c r="D28" s="17" t="inlineStr">
+        <is>
+          <t>adzuna</t>
+        </is>
+      </c>
+      <c r="E28" s="17" t="inlineStr">
+        <is>
+          <t>usajobs} with cheap per-provider probes (1-token Claude Haiku call, single-result JSearch / Adzuna / USAJobs queries) and a per-IP sliding-window rate limit (10 / min, env-overridable via BYOK_TEST_RATE) so the endpoint can't be used as an anonymous key-validator service. **App config:** jobpilot/app.py tightened _rate_limit_check() to a fast-path return for non-demo emails — real users pay their own Anthropic bill so the server has no reason to limit them; demo cap is unchanged at 10/day. Registered the new byok_bp blueprint. **Tests:** tests/test_auth_smoke.py added test_tailor_requires_byok_header_for_real_user (asserts 400 + byok_required + header fields when a real-user JWT hits /api/tailor with no X-Anthropic-Key and no server env var) and test_byok_test_route_rejects_unknown_provider. pytest now 9/9 green. **Deferred to Phase 2B (next turn):** (1) thread BYOK creds (X-RapidAPI-Key, X-Adzuna-App-Id/Key, X-USAJobs-Email/Key) down through core/job_scraper.py search_jsearch / search_adzuna / search_usajobs (ThreadPoolExecutor means flask.g doesn't propagate — must pass explicit kwargs); (2) frontend Settings modal in jobpilot/templates/index.html + jobpilot/static/js/app.js with AES-GCM-encrypted localStorage.jp_keys keyed on Google sub + per-field "Test" button + central apiHeaders() helper to refactor all ~40 authenticated fetch sites. Pausing here for user review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>**Phase 2B — BYOK end-to-end (job-board credentials + Settings UI + auto-open-on-failure).** Completed everything Phase 2A explicitly deferred. **Backend (scraper credential threading):** jobpilot/core/byok.py now also exports JobSearchCreds(frozen=True) (5 Optional[str] fields: rapidapi_key, adzuna_app_id, adzuna_app_key, usajobs_email, usajobs_key) and read_job_search_creds(email) which resolves each field via get_api_key() on the request thread. The key insight: flask.g does **not** propagate into ThreadPoolExecutor workers, so jobpilot/core/job_scraper.py was refactored — search_jsearch / search_adzuna / search_usajobs each take explicit keyword-only api_key / app_id / app_key / email parameters (env-var fallback retained for the demo path), and search_all_platforms(..., *, creds: JobSearchCreds</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="inlineStr">
+        <is>
+          <t>None = None) destructures the 5 strings up-front so the lambdas inside the ThreadPoolExecutor capture plain strings, not flask.g. jobpilot/routes/jobs.py /api/jobs now reads email = getattr(g, "email", None) + creds = read_job_search_creds(email) on the request thread and passes creds=creds into the scraper; the quota counter (#46) also moved to check creds.rapidapi_key / creds.adzuna_app_id so usage stats reflect what was actually called for *this* user. One-line env-var name fix in jobpilot/routes/byok.py (USAJOBS_USER_EMAIL → USAJOBS_EMAIL) so the /api/byok/test?provider=usajobs demo-fallback probe matches .env.example. **Frontend (Settings UI + 7-site fetch wiring):** jobpilot/static/js/app.js gained a full BYOK module (~170 lines): AES-GCM-encrypted localStorage.jp_byok_v1 blob ({v:1, iv, ct} JSON, base64-encoded), 256-bit key derived via PBKDF2-SHA-256 with 200k iters and salt "jobpilot-byok-v1", seed = user email (documented in-code as not zero-knowledge — sufficient against shared-device casual snooping, not against a determined attacker with the same email). Public API: byokInit() (called fire-and-forget after checkHealth()), byokSave(plain), byokClear() (called from clearLoginSession()), byokTestProvider(provider, candidateHeaders). The new _byokHeaders() is composed into authHeaders() so every authenticated fetch site automatically forwards X-Anthropic-Key / X-Claude-Model / X-RapidAPI-Key / X-Adzuna-App-Id / X-Adzuna-App-Key / X-USAJobs-Email / X-USAJobs-Key with zero per-call changes. Settings modal handlers (openSettingsModal / closeSettingsModal / byokTestFromForm(provider) / byokSaveFromForm) + auto-open-on-failure helper handleByokRequired(d) (toasts "Open Settings…" and pops the modal when the backend returns {byok_required: true}). The 7 Claude-touching fetch sites now check if (handleByokRequired(d)) return; immediately after await r.json(), each with correct state-machine rollback (e.g. generate-resume restores st.state = "gen_form", tailor restores "idle", chat-instruction pops the in-flight user message, ATS-assist resets atsAssistWorking / atsAssistMode). jobpilot/templates/index.html adds: (a) #byok-settings-btn topbar button (gear icon, gated on revealTopbarUser()); (b) #byok-overlay modal with 7 inputs (byok-anthropic, byok-claude-model, byok-rapidapi, byok-adzuna-id, byok-adzuna-key, byok-usajobs-email, byok-usajobs-key), per-provider **Test** buttons + status pills (byok-status-{anthropic</t>
+        </is>
+      </c>
+      <c r="D29" s="17" t="inlineStr">
+        <is>
+          <t>jsearch</t>
+        </is>
+      </c>
+      <c r="E29" s="17" t="inlineStr">
+        <is>
+          <t>adzuna</t>
         </is>
       </c>
     </row>
